--- a/Content/ProjectVD/DataTable/InventoryItemInfoList.xlsx
+++ b/Content/ProjectVD/DataTable/InventoryItemInfoList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DC7FBE-B9EC-4BD7-B975-4DD903340CE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6CA603-490C-412B-B7B3-390A667290C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,18 @@
   </si>
   <si>
     <t>empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TwoHandSword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양손검</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,8 +408,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="29.19921875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -447,6 +462,23 @@
         <v>99</v>
       </c>
       <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Content/ProjectVD/DataTable/InventoryItemInfoList.xlsx
+++ b/Content/ProjectVD/DataTable/InventoryItemInfoList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6CA603-490C-412B-B7B3-390A667290C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A69D13-32EF-498B-B0AB-3F5C6DCC32F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,22 @@
   </si>
   <si>
     <t>양손검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealingPosition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TwoHandSword</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -408,13 +424,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
+    <col min="3" max="3" width="27.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -422,16 +439,19 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -439,16 +459,19 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -456,16 +479,19 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>99</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -473,12 +499,15 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Content/ProjectVD/DataTable/InventoryItemInfoList.xlsx
+++ b/Content/ProjectVD/DataTable/InventoryItemInfoList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A69D13-32EF-498B-B0AB-3F5C6DCC32F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E70E60F-D907-4721-A1D6-0C7C9947E2EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,23 +82,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>양손검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ItemName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealingPosition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TwoHandSword</t>
+    <t>한손검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복물약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두손검</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -439,7 +435,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
@@ -459,7 +455,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -479,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -499,10 +495,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>1</v>
